--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96156</v>
+        <v>96159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92454</v>
+        <v>92457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330090</v>
       </c>
       <c r="B2" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96159</v>
+        <v>96185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92457</v>
+        <v>92483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130339295</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96185</v>
+        <v>96186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92483</v>
+        <v>92484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96186</v>
+        <v>96187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92484</v>
+        <v>92485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130330090</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96187</v>
+        <v>96189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92485</v>
+        <v>92487</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91780</v>
+        <v>91782</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>130339295</v>
       </c>
       <c r="B6" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130330614</v>
       </c>
       <c r="B3" t="n">
-        <v>96189</v>
+        <v>96193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>130331499</v>
       </c>
       <c r="B4" t="n">
-        <v>92487</v>
+        <v>92491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1223,6 +1223,246 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131580322</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57889</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogslund, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6331100</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131580193</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92552</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>757</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Apelsinticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hapalopilus aurantiacus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogslund, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483720</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6330944</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Porer 3 per mm. Mörkröd med KOH.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Barklös låga # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Fogelström, Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62705-2025 artfynd.xlsx
+++ b/artfynd/A 62705-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130330090</v>
+        <v>130331499</v>
       </c>
       <c r="B2" t="n">
-        <v>58236</v>
+        <v>92640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>757</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granhult, Gårdgölen 200 m. SV., Sm</t>
+          <t>Gårdsgölen, Granhult 200 m. SV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483704</v>
+        <v>483721</v>
       </c>
       <c r="R2" t="n">
-        <v>6330933</v>
+        <v>6330941</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,19 +754,14 @@
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-12-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På granlåga  i gles äldre gran-tallskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,60 +789,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130330614</v>
+        <v>131580193</v>
       </c>
       <c r="B3" t="n">
-        <v>96210</v>
+        <v>92716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>757</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gårdsgölen, Granhult, 200 m. VSV, Sm</t>
+          <t>Skogslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483672</v>
+        <v>483720</v>
       </c>
       <c r="R3" t="n">
-        <v>6330979</v>
+        <v>6330944</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,17 +857,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en del av ett klippblock.</t>
+          <t>Porer 3 per mm. Mörkröd med KOH.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,71 +880,87 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Barklös låga # Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Uno Pettersson, Elin Kannerby</t>
+          <t>Per Fogelström, Uno Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130331499</v>
+        <v>130330614</v>
       </c>
       <c r="B4" t="n">
-        <v>92506</v>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>757</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gårdsgölen, Granhult 200 m. SV, Sm</t>
+          <t>Gårdsgölen, Granhult, 200 m. VSV, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483721</v>
+        <v>483672</v>
       </c>
       <c r="R4" t="n">
-        <v>6330941</v>
+        <v>6330979</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -995,7 +997,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På granlåga  i gles äldre gran-tallskog.</t>
+          <t>På en del av ett klippblock.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1028,7 @@
         <v>130339296</v>
       </c>
       <c r="B5" t="n">
-        <v>91797</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1120,35 +1122,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130339295</v>
+        <v>131580322</v>
       </c>
       <c r="B6" t="n">
-        <v>58023</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
@@ -1163,13 +1169,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483736</v>
+        <v>483615</v>
       </c>
       <c r="R6" t="n">
-        <v>6330924</v>
+        <v>6331100</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,12 +1199,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,39 +1229,39 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Uno Pettersson</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131580322</v>
+        <v>130330090</v>
       </c>
       <c r="B7" t="n">
-        <v>57911</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1255,27 +1271,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skogslund, Sm</t>
+          <t>Granhult, Gårdgölen 200 m. SV., Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483615</v>
+        <v>483704</v>
       </c>
       <c r="R7" t="n">
-        <v>6331100</v>
+        <v>6330933</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1302,22 +1318,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,49 +1348,54 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Uno Pettersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Fogelström</t>
+          <t>Uno Pettersson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131580193</v>
+        <v>131580341</v>
       </c>
       <c r="B8" t="n">
-        <v>92579</v>
+        <v>58250</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>757</v>
+        <v>103019</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Apelsinticka</t>
+          <t>Stjärtmes</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hapalopilus aurantiacus</t>
+          <t>Aegithalos caudatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Rostk.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,13 +1403,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483720</v>
+        <v>483615</v>
       </c>
       <c r="R8" t="n">
-        <v>6330944</v>
+        <v>6331100</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1415,14 +1436,19 @@
           <t>2026-03-11</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Porer 3 per mm. Mörkröd med KOH.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,24 +1457,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Barklös låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1458,10 +1468,234 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Fogelström, Uno Pettersson</t>
+          <t>Per Fogelström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130339295</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Skogslund, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483736</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6330924</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131584635</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skogslund, 400 m söder., Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483690</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6330959</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Växjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Asa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Uno Pettersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Uno Pettersson, Per Fogelström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
